--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB84BA-4AB3-4DF1-8E91-7ABE8EC65BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -20,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
   <si>
     <t>48978</t>
   </si>
@@ -148,9 +154,6 @@
     <t>436314</t>
   </si>
   <si>
-    <t>436305</t>
-  </si>
-  <si>
     <t>436311</t>
   </si>
   <si>
@@ -223,7 +226,7 @@
     <t>Tipo de acción determinada por el órgano fiscalizador</t>
   </si>
   <si>
-    <t>Servidor(a) público(a) y/o área responsable de recibir los resultados</t>
+    <t>Nombre de la persona servidora pública y/o área del sujeto obligado responsable o encargada de recibir los resultados</t>
   </si>
   <si>
     <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
@@ -244,22 +247,19 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Del 01/01/2022 al 31/12/2022</t>
+    <t>Del 01/01/2023 al 31/12/2023</t>
   </si>
   <si>
     <t>Auditoría externa</t>
@@ -268,32 +268,40 @@
     <t>Financiera</t>
   </si>
   <si>
-    <t>UAG-AOR-062-2023-29-U006</t>
-  </si>
-  <si>
-    <t>Secretaría de la Función Pública</t>
-  </si>
-  <si>
-    <t>UAG-AOR-062-2023-29-U006 
-CGI2023-09</t>
-  </si>
-  <si>
-    <t>SFCC/200/087/2023</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Participaciones Federales a Entidades Federativas</t>
+    <t>OFS/2255/2023</t>
+  </si>
+  <si>
+    <t>Organo de fiscalización Superior del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Orden de auditoría
+Oficio No. OFS/2255/2023</t>
+  </si>
+  <si>
+    <t>Anexo I</t>
+  </si>
+  <si>
+    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2023.</t>
   </si>
   <si>
     <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 1000, 2000, 3000, 4000 y 5000.</t>
   </si>
   <si>
-    <t>Artículo 74 fraccion VI y 79 de la Constitucion Politica de los Estados Unidos Mexicanos; fracciones II, VIII,IX, X, XI, XVI, XVIII y XXX; 6,9,14, fracciones I, III y IV; 17, fracciones I, VI, VII, VIII, XI, XII, XXVI, XXVII y XXVIII; 22, 23, 28, 29, 47, 48, 49, 58 y 67,  y demas relativos de Fiscalizacion y Rendicion de Cuentas de la Federacion; 8, el Presupuesto de Egresos de la Federacion para el ejercicio fiscal 2020, 2, 3, 12 fraccion III del Reglamento Interior de la Auditoria  Superior de la Federacion.</t>
-  </si>
-  <si>
-    <t>Subsidios Federales</t>
+    <t>Artículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
+  </si>
+  <si>
+    <t>OFS/1851/2024</t>
+  </si>
+  <si>
+    <t>https://www.ofstlaxcala.gob.mx/informes_2023</t>
+  </si>
+  <si>
+    <t>Recursos recaudados
+Participaciones estatales
+Remanentes de ejercicios anteriores y/o federales</t>
+  </si>
+  <si>
+    <t>111</t>
   </si>
   <si>
     <t>Dirección Administrativa 
@@ -304,93 +312,16 @@
 Departamento de contabilidad</t>
   </si>
   <si>
-    <t>Departamento de contabilidad</t>
-  </si>
-  <si>
-    <t>1877</t>
-  </si>
-  <si>
-    <t>Auditoria Superior de la Federación</t>
-  </si>
-  <si>
-    <t>2022-1877-AFITA 
-1877/2022</t>
-  </si>
-  <si>
-    <t>AEGF/3042/2023</t>
-  </si>
-  <si>
-    <t>Fondo de aportaciones múltiples (FAM)</t>
-  </si>
-  <si>
-    <t>Ejercicio y aplicación de los recursos públicos federales, de los capitulo 5000</t>
-  </si>
-  <si>
-    <t>Participaciones Federales</t>
-  </si>
-  <si>
-    <t>OFS/3651/2022</t>
-  </si>
-  <si>
-    <t>Organo de fiscalización Superior del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Orden de auditoría
-Oficio No. OFS/3651/2022</t>
-  </si>
-  <si>
-    <t>Anexo I</t>
-  </si>
-  <si>
-    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2022.</t>
-  </si>
-  <si>
-    <t>Artículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
-  </si>
-  <si>
-    <t>Recursos recaudados
-Participaciones estatales
-Remanentes de ejercicios anteriores y/o federales</t>
-  </si>
-  <si>
-    <t>1893</t>
-  </si>
-  <si>
-    <t>Acta 2022-1893-AFITA</t>
-  </si>
-  <si>
-    <t>AEGF/3085/2023</t>
-  </si>
-  <si>
-    <t>Subisidios Federales para Organismos Descentralizados  Estatales, Politecnica y Pública con Apoyo Solidario (U006) de la Cuenta Pública 2022</t>
-  </si>
-  <si>
-    <t>DDEB61CA64F4120265CA61B3EBEE7FBC</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>03/07/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la solicitud de información adicional, cabe señalar que se encuentra en proceso la auditoría mencionada.</t>
-  </si>
-  <si>
-    <t>0B4BB353E9FD9635E63D7927C8AF14C7</t>
-  </si>
-  <si>
-    <t>OFS/1403/2023
- Del 01 de Octubre al 31 de Diciembre 2022</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>37</t>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>https://www.ofstlaxcala.gob.mx/Fracci%C3%B3n%20XXIV</t>
   </si>
   <si>
     <t>Dirección Administrativa
@@ -398,19 +329,30 @@
 Subdirección Financiera</t>
   </si>
   <si>
-    <t>Durante el período del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención a la solicitud de información adicional.</t>
-  </si>
-  <si>
-    <t>366AD54B37A04A72F75DFAB59D26C1F2</t>
-  </si>
-  <si>
-    <t>1EFE4C4239DB1DB34E1DB289D2588E90</t>
+    <t>61958D93A83AB0BEDE3F113928151CCF</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>02/07/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de marzo de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
+Asimismo los hallazgos emitidos seran debidamente integrados en el informe de resultados Individuales a la Comisión a, para su dictaminación y posterior aprobación o no por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
+  </si>
+  <si>
+    <t>6BD56FEE49B811F2C87A0BE8C468A1C0</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de enero de 2024 al 30 de marzo de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
+Asimismo los hallazgos emitidos seran debidamente integrados en el informe de resultados Individuales a la Comisión a, para su dictaminación y posterior aprobación o no por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
   </si>
   <si>
     <t>Auditoría interna</t>
-  </si>
-  <si>
-    <t>Hombre</t>
   </si>
   <si>
     <t>Mujer</t>
@@ -419,7 +361,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -515,6 +457,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -530,44 +475,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -595,14 +540,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -630,6 +592,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -641,175 +620,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -817,7 +772,7 @@
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="55.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -828,27 +783,26 @@
     <col min="17" max="17" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="54.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="52.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="57.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="100.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="77.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="49.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="205.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -865,7 +819,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -880,7 +834,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -966,16 +920,13 @@
         <v>9</v>
       </c>
       <c r="AD4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1066,13 +1017,10 @@
       <c r="AE5" t="s">
         <v>43</v>
       </c>
-      <c r="AF5" t="s">
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1104,498 +1052,292 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
     </row>
-    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="W7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AA7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AC7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AD7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AE7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AE7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AF7" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="T8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>91</v>
       </c>
       <c r="X8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>91</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF10" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF11" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="A6:AE6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1604,10 +1346,10 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G193">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G197" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X193">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X197" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_223</formula1>
     </dataValidation>
   </dataValidations>
@@ -1616,18 +1358,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1636,18 +1378,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIV/LTAIPT_A63F24.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AB84BA-4AB3-4DF1-8E91-7ABE8EC65BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1815ED4D-03CC-477C-9F08-44AA5D4E4363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="111">
   <si>
     <t>48978</t>
   </si>
@@ -253,7 +253,16 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>F05A99639CC1819DD94AC47A955C95EA</t>
+  </si>
+  <si>
     <t>2024</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
   </si>
   <si>
     <t>2023</t>
@@ -329,27 +338,35 @@
 Subdirección Financiera</t>
   </si>
   <si>
-    <t>61958D93A83AB0BEDE3F113928151CCF</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de marzo de 2024 al 30 de junio de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
-Asimismo los hallazgos emitidos seran debidamente integrados en el informe de resultados Individuales a la Comisión a, para su dictaminación y posterior aprobación o no por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
-  </si>
-  <si>
-    <t>6BD56FEE49B811F2C87A0BE8C468A1C0</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2024 al 30 de marzo de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
-Asimismo los hallazgos emitidos seran debidamente integrados en el informe de resultados Individuales a la Comisión a, para su dictaminación y posterior aprobación o no por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
+    <t>02/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2024 al 30 de septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
+Asimismo los hallazgos emitidos han sido integrados en el informe de resultados Individuales a la Comisión a, por lo que la cuenta pública del ejercicio fiscal 2023, se encuentra  aprobada por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.
+Considerando la revision del ejercicio fiscal 2023, culminada.</t>
+  </si>
+  <si>
+    <t>CC75623FD9CF788CD64DFC8EA7897FD3</t>
+  </si>
+  <si>
+    <t>Del 01/01/2024 al 31/12/2024</t>
+  </si>
+  <si>
+    <t>OFS/2544/2024</t>
+  </si>
+  <si>
+    <t>Orden de auditoría
+Oficio No. OFS/2544/2024</t>
+  </si>
+  <si>
+    <t>Ingreso, Egreso, el manejo , la custodia y aplicación de fondos, recursos y remanentes de ejercicios anteriores correspondiente al ejercicio fiscal 2024.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2024 al 30 de septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala,  ha dado atención y respuesta a los requerimientos realizados por la autoridad fiscalizadora.
+Se informa que la auditoría ha iniciado siete de agosto del ejercicio fiscal 2024, por lo que se considera en PROCESO, por lo que una vez sean emitidos los hallazgos, seran debidamente integrados en el informe de resultados Individuales a la Comisión a, para su dictaminación y posterior aprobación o no por el Pleno del Congreso del Estado de Tlaxcala, en apego a lo señalado en el Capitulo I, Del informe individual, articulo 46, 47, 48, 51 y 52 de  Ley de Fiscalización Superior y Rendición de Cuenta del Estado de Tlaxcala y sus Municipios yArtículos 116 fracción II párrafo sexto, articulo 134 párrafo segundo de la Constitución Política de los Estados Unidos Mexicanos, articulo 54 fracción XVII inciso A y B, 104 y 105 de la Constitución Política del Estado Libre y Soberano del Estado de Tlaxcala, articulo 1 fracción I, 3, 4, 5, 6, 22, 23, 24, 25, 27, 28, 29, 30, 31, 32, 74 fracciones I, II, XI, XIV, XVI, XVII, 8 fracciones I, V, VI, VIII del Reglemento Interior del órgano de Fiscalización Superior del Congreso del Estado de Tlaxcala publicado en el periodico oficial número uno Extraordinario de fecha veinte de marzo del dos mil veinte; numerales 1.1, 1.4 y 4.1 de las Normas Profesionales de Auditoría del Sistema Nacional de Fiscalización y coforme al decreto 244 de fecha 09 de Noviembre de 2016, publicado en el Periodico Oficial del Gobierno del Estado de Tlaxcala.</t>
   </si>
   <si>
     <t>Auditoría interna</t>
@@ -1147,91 +1164,91 @@
     </row>
     <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>100</v>
@@ -1245,94 +1262,94 @@
         <v>102</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1364,12 +1381,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1384,12 +1401,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
